--- a/startAndEnd.xlsx
+++ b/startAndEnd.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,8 +439,6 @@
           <t>hello:</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -448,12 +446,6 @@
           <t>#   start: Устраняем неполадки с СБП. Пожалуйста, выполните перевод позднее.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Устраняем неполадки с СБП. Пожалуйста, выполните перевод позднее.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -461,8 +453,6 @@
           <t xml:space="preserve">  unauthorized:</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -470,8 +460,11 @@
           <t xml:space="preserve">    - Приветствую вас! На связи Уралсиб-бот.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Приветствую вас! На связи Уралсиб-бот.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -479,8 +472,11 @@
           <t xml:space="preserve">    - Рад приветствовать вас! С вами Уралсиб-бот.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Рад приветствовать вас! С вами Уралсиб-бот.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -488,8 +484,11 @@
           <t xml:space="preserve">    - Здравствуйте! На связи Уралсиб-бот.</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Здравствуйте! На связи Уралсиб-бот.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -497,8 +496,6 @@
           <t xml:space="preserve">  authorized:</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -511,7 +508,6 @@
           <t>Приветствую вас, {{ $session.name }}! На связи Уралсиб-бот.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -519,8 +515,11 @@
           <t xml:space="preserve">    - Рад приветствовать вас, {{ $session.name }}! С вами Уралсиб-бот.</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Рад приветствовать вас, {{ $session.name }}! С вами Уралсиб-бот.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -528,8 +527,11 @@
           <t xml:space="preserve">    - Здравствуйте, {{ $session.name }}! Я Уралсиб-бот, цифровой помощник банка.</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Здравствуйте, {{ $session.name }}! Я Уралсиб-бот, цифровой помощник банка.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -537,8 +539,6 @@
           <t xml:space="preserve">  oldApp:</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -546,8 +546,6 @@
           <t xml:space="preserve">    ios:</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -555,8 +553,16 @@
           <t xml:space="preserve">      Ваша версия приложения устарела. Чтобы использовать максимум преимуществ, установите веб-версию. В браузере Safari перейдите по ссылке и следуйте [инструкции](https://uralsib.ru/online/ios)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ваша версия приложения устарела. Чтобы использовать максимум преимуществ, установите веб-версию. В браузере Safari перейдите по ссылке и следуйте [инструкции](https://uralsib.ru/online/ios).</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>добавлена точка в конце предложения</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -564,8 +570,6 @@
           <t xml:space="preserve">    android:</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -573,8 +577,16 @@
           <t xml:space="preserve">      Ваша версия приложения устарела. Чтобы использовать максимум преимуществ, [обновите его](https://uralsib.ru/online/android)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ваша версия приложения устарела. Чтобы использовать максимум преимуществ, [обновите его](https://uralsib.ru/online/android).</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>добавлена точка в конце предложения</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -582,8 +594,6 @@
           <t xml:space="preserve">  preProcess:</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -591,8 +601,11 @@
           <t xml:space="preserve">    - Приветствую вас!</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Приветствую вас!</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -602,10 +615,9 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - Здравствуйте!</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>Здравствуйте!</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -613,26 +625,19 @@
           <t xml:space="preserve">    - Рад приветствовать вас!</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Пустой текст</t>
-        </is>
-      </c>
-    </row>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Рад приветствовать вас!</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
           <t>howCanIHelpYou:</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -640,8 +645,6 @@
           <t xml:space="preserve">  firstReplies:</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -649,8 +652,11 @@
           <t xml:space="preserve">    - Пожалуйста, уточните, чем я могу вам помочь?</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Пожалуйста, уточните, чем я могу вам помочь?</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -658,8 +664,11 @@
           <t xml:space="preserve">    - Готов вам помочь. Задайте ваш вопрос, пожалуйста.</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Готов вам помочь. Задайте ваш вопрос, пожалуйста.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -667,8 +676,11 @@
           <t xml:space="preserve">    - Напишите свой вопрос, я помогу.</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Напишите свой вопрос, я помогу.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -676,8 +688,6 @@
           <t xml:space="preserve">  buttons:</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -685,8 +695,6 @@
           <t xml:space="preserve">    - text: "Карты"</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -694,8 +702,6 @@
           <t xml:space="preserve">      transition: "/CardsConsultation/Card"</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -703,8 +709,6 @@
           <t xml:space="preserve">    - text: "Кредиты"</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -712,8 +716,6 @@
           <t xml:space="preserve">      transition: "/LoansConsultation/Loan"</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -721,8 +723,6 @@
           <t xml:space="preserve">    - text: "Вклады"</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -730,8 +730,6 @@
           <t xml:space="preserve">      transition: "/Deposits/Deposit"</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -739,8 +737,6 @@
           <t xml:space="preserve">    - text: "Платежи и переводы"</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -748,8 +744,6 @@
           <t xml:space="preserve">      transition: "/PaymentsAndTransfer/MoneyTransfer"</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -757,8 +751,6 @@
           <t xml:space="preserve">    - text: "Навигация в системе"</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -766,8 +758,6 @@
           <t xml:space="preserve">      transition: "/MobileAppNavigation/DBONavigation"</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -775,12 +765,6 @@
           <t xml:space="preserve">    # TODO from main</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t># TODO from main</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -788,8 +772,6 @@
           <t xml:space="preserve">    # - text: "Дебетовые карты"</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -797,8 +779,6 @@
           <t xml:space="preserve">    #   transition: "/CardQuestion/Common/DebitCard"</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -806,8 +786,6 @@
           <t xml:space="preserve">    # - text: "Кредиты"</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -815,8 +793,6 @@
           <t xml:space="preserve">    #   transition: "/Loan/Common"</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -824,8 +800,6 @@
           <t xml:space="preserve">    # - text: "Вклады"</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -833,12 +807,6 @@
           <t xml:space="preserve">    #   transition: "/Deposits/Deposit"</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    #   transition: "/Deposits/Deposit"</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -846,12 +814,6 @@
           <t xml:space="preserve">    # - text: "Платежи и переводы"</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Платежи и переводы</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -859,12 +821,6 @@
           <t xml:space="preserve">    #   transition: "/PaymentsAndTransfer/Common"</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>#   transition: "/PaymentsAndTransfer/Common"</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -872,8 +828,6 @@
           <t xml:space="preserve">    # - text: "Навигация в системе"</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -881,26 +835,14 @@
           <t xml:space="preserve">    #   transition: "/MobileAppNavigation/DBONavigation"</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Пустой текст</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
           <t>dontHaveQuestions:</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -908,26 +850,19 @@
           <t xml:space="preserve">  - Понял вас!</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Пустой текст</t>
-        </is>
-      </c>
-    </row>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Понял вас!</t>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
           <t>somethingElse:</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -935,8 +870,6 @@
           <t xml:space="preserve">  reply:</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -944,8 +877,11 @@
           <t xml:space="preserve">      - Хотите спросить что-то еще?</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Хотите спросить что-то еще?</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -953,8 +889,11 @@
           <t xml:space="preserve">      - Могу ли я помочь чем-то еще?</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Могу ли я помочь чем-то еще?</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -962,8 +901,11 @@
           <t xml:space="preserve">      - Желаете задать еще вопрос?</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Желаете задать еще вопрос?</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -971,8 +913,6 @@
           <t xml:space="preserve">  debitButton:</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -980,8 +920,6 @@
           <t xml:space="preserve">    - text: "Назад к списку дебетовых карт"</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -989,12 +927,6 @@
           <t xml:space="preserve">      transition: "/DebitCards/DebitCard/AskCardType"</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>transition: "/DebitCards/DebitCard/AskCardType"</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1002,8 +934,6 @@
           <t xml:space="preserve">  creditButton:</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1011,12 +941,6 @@
           <t xml:space="preserve">    - text: "Назад к списку кредитных карт"</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Назад к списку кредитных карт</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1024,26 +948,14 @@
           <t xml:space="preserve">      transition: "/CreditCards/CreditCard/AskCardType"</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Пустой текст</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
           <t>goodbye:</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1051,8 +963,11 @@
           <t xml:space="preserve">  - Благодарю за обращение! Всего доброго!</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Благодарю за обращение! Всего доброго!</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1062,10 +977,9 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>- Спасибо вам за обращение! Всего доброго, до свидания!</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>Спасибо вам за обращение! Всего доброго, до свидания!</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
